--- a/data/production/production_2026-W39.xlsx
+++ b/data/production/production_2026-W39.xlsx
@@ -423,7 +423,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G34"/>
+  <dimension ref="A1:G35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -488,12 +488,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>AU-316916</t>
+          <t>AU-569417</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Owen Sorensen</t>
+          <t>Caleb Whitfield</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -503,11 +503,11 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Renewal</t>
+          <t xml:space="preserve"> Renewal</t>
         </is>
       </c>
       <c r="G4" t="n">
-        <v>1618.21</v>
+        <v>1277.82</v>
       </c>
     </row>
     <row r="5">
@@ -516,31 +516,31 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Aisha Bello</t>
+          <t>Luis Ortega</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>CM-414849</t>
+          <t>HO-916146</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Grace Delgado</t>
+          <t>Maria Lopez</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Commercial</t>
+          <t xml:space="preserve">Home </t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>New</t>
+          <t>Renewal</t>
         </is>
       </c>
       <c r="G5" t="n">
-        <v>5440.91</v>
+        <v>3020.16</v>
       </c>
     </row>
     <row r="6">
@@ -549,22 +549,22 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Grant Fowler</t>
+          <t xml:space="preserve"> Maya Chen</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>AU-306909</t>
+          <t>HO-384580</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Olivia Hartley</t>
+          <t>Clara Pryor</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Auto</t>
+          <t>Home</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -573,7 +573,7 @@
         </is>
       </c>
       <c r="G6" t="n">
-        <v>1883.87</v>
+        <v>2966.17</v>
       </c>
     </row>
     <row r="7">
@@ -582,31 +582,31 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t xml:space="preserve">Grant Fowler </t>
+          <t>Maya Chen</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>AU-375097</t>
+          <t>HO-569426</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Nora Ashby</t>
+          <t>Olivia Hartley</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Auto</t>
+          <t>Home</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>New</t>
+          <t>Renewal</t>
         </is>
       </c>
       <c r="G7" t="n">
-        <v>1195.61</v>
+        <v>2944.22</v>
       </c>
     </row>
     <row r="8">
@@ -615,22 +615,22 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Grant Fowler</t>
+          <t>Tom Becker</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>AU-705393</t>
+          <t>LF-971118</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Alma Ashby</t>
+          <t>Mila Tanaka</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Auto</t>
+          <t>Life</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -639,64 +639,64 @@
         </is>
       </c>
       <c r="G8" t="n">
-        <v>2028.49</v>
+        <v>1443.59</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="n">
-        <v>46286</v>
+        <v>46287</v>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Luis Ortega</t>
+          <t>Aisha Bello</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>AU-457137</t>
+          <t>AU-917151</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Clara Haines</t>
+          <t>Maria Novak</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Auto</t>
+          <t xml:space="preserve">Auto </t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>New</t>
+          <t>Renewal</t>
         </is>
       </c>
       <c r="G9" t="n">
-        <v>1555.63</v>
+        <v>955.48</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="n">
-        <v>46286</v>
+        <v>46287</v>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Luis Ortega</t>
+          <t>Aisha Bello</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>AU-694316</t>
+          <t>HO-590156</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Clara Pryor</t>
+          <t>Elena Mbeki</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Auto</t>
+          <t>Home</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -705,26 +705,26 @@
         </is>
       </c>
       <c r="G10" t="n">
-        <v>2151.5</v>
+        <v>1750.68</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="n">
-        <v>46286</v>
+        <v>46287</v>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Luis Ortega</t>
+          <t>Aisha Bello</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>LF-134500</t>
+          <t>LF-453145</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Olivia Hartley</t>
+          <t>Leah Okafor</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -734,63 +734,63 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Renewal</t>
+          <t>New</t>
         </is>
       </c>
       <c r="G11" t="n">
-        <v>1833.67</v>
+        <v>2176.31</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="n">
-        <v>46286</v>
+        <v>46287</v>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Maya Chen</t>
+          <t>Aisha Bello</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>HO-831105</t>
+          <t>LF-970326</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Grace Delgado</t>
+          <t>Ruby Ferreira</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Home</t>
+          <t>Life</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Renewal</t>
+          <t>New</t>
         </is>
       </c>
       <c r="G12" t="n">
-        <v>1727.69</v>
+        <v>2284.31</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="n">
-        <v>46286</v>
+        <v>46287</v>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Maya Chen</t>
+          <t>Grant Fowler</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>HO-922478</t>
+          <t>HO-545336</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Leah Novak</t>
+          <t>Victor Petrov</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -803,15 +803,13 @@
           <t>Renewal</t>
         </is>
       </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>$2,245.72</t>
-        </is>
+      <c r="G13" t="n">
+        <v>1175.47</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="n">
-        <v>46286</v>
+        <v>46287</v>
       </c>
       <c r="B14" t="inlineStr">
         <is>
@@ -820,17 +818,17 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>LF-842776</t>
+          <t>LF-744413</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Leah Okafor</t>
+          <t>Owen Kowal</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>LIFE</t>
+          <t>Life</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -839,31 +837,31 @@
         </is>
       </c>
       <c r="G14" t="n">
-        <v>1609.5</v>
+        <v>2254.52</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="n">
-        <v>46287</v>
+        <v>46288</v>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Aisha Bello</t>
+          <t>GRANT FOWLER</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>HO-190025</t>
+          <t>AU-445474</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Sofia Pryor</t>
+          <t>Caleb Whitfield</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Home</t>
+          <t>auto</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -872,31 +870,31 @@
         </is>
       </c>
       <c r="G15" t="n">
-        <v>1911.55</v>
+        <v>1369.18</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="n">
-        <v>46287</v>
+        <v>46288</v>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Aisha Bello</t>
+          <t xml:space="preserve">Grant Fowler </t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>LF-678719</t>
+          <t>LF-750912</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Olivia Delgado</t>
+          <t>Grace Delgado</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Life</t>
+          <t xml:space="preserve">Life </t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -905,45 +903,45 @@
         </is>
       </c>
       <c r="G16" t="n">
-        <v>1063.43</v>
+        <v>2129.2</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="n">
-        <v>46287</v>
+        <v>46288</v>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Grant Fowler</t>
+          <t>Luis Ortega</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>LF-412170</t>
+          <t>AU-611771</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Grace Delgado</t>
+          <t>Maria Ashby</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Life</t>
+          <t>Auto</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>New</t>
+          <t xml:space="preserve">New </t>
         </is>
       </c>
       <c r="G17" t="n">
-        <v>794.59</v>
+        <v>1449.84</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="n">
-        <v>46287</v>
+        <v>46288</v>
       </c>
       <c r="B18" t="inlineStr">
         <is>
@@ -952,17 +950,17 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>AU-928897</t>
+          <t>CM-375769</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Theo Moreau</t>
+          <t>Maria Novak</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Auto</t>
+          <t>Commercial</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -970,62 +968,60 @@
           <t>New</t>
         </is>
       </c>
-      <c r="G18" t="inlineStr">
-        <is>
-          <t>$2,033.41</t>
-        </is>
+      <c r="G18" t="n">
+        <v>7129.3</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="n">
-        <v>46287</v>
+        <v>46288</v>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Maya Chen</t>
+          <t>Maya Chen</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>AU-679549</t>
+          <t>CM-414006</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Theo Moreau</t>
+          <t>Victor Petrov</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Auto</t>
+          <t>commercial</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Renewal</t>
+          <t>New</t>
         </is>
       </c>
       <c r="G19" t="n">
-        <v>1565.13</v>
+        <v>3902.99</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="n">
-        <v>46287</v>
+        <v>46288</v>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Maya Chen</t>
+          <t>Priya Raman</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>CM-212214</t>
+          <t>CM-111619</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Maria Ashby</t>
+          <t>Isaac Holloway</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -1039,7 +1035,7 @@
         </is>
       </c>
       <c r="G20" t="n">
-        <v>8822.91</v>
+        <v>3235.38</v>
       </c>
     </row>
     <row r="21">
@@ -1048,31 +1044,31 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Aisha Bello</t>
+          <t>Priya Raman</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>LF-779445</t>
+          <t>CM-967377</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Alma Ashby</t>
+          <t>Jonah Quill</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Life</t>
+          <t>Commercial</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>New</t>
+          <t>Renewal</t>
         </is>
       </c>
       <c r="G21" t="n">
-        <v>818.66</v>
+        <v>8799.860000000001</v>
       </c>
     </row>
     <row r="22">
@@ -1081,22 +1077,22 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Luis Ortega</t>
+          <t>Priya Raman</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>HO-847332</t>
+          <t>LF-163440</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Olivia Delgado</t>
+          <t>Ivy Hartley</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Home</t>
+          <t>life</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1104,8 +1100,10 @@
           <t>Renewal</t>
         </is>
       </c>
-      <c r="G22" t="n">
-        <v>2972.71</v>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>$898.47</t>
+        </is>
       </c>
     </row>
     <row r="23">
@@ -1114,22 +1112,22 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Maya Chen</t>
+          <t>Priya Raman</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>HO-471658</t>
+          <t>LF-711698</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Marcus Novak</t>
+          <t>Felix Tanaka</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>home</t>
+          <t>Life</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1137,10 +1135,8 @@
           <t>Renewal</t>
         </is>
       </c>
-      <c r="G23" t="inlineStr">
-        <is>
-          <t>$1,678.22</t>
-        </is>
+      <c r="G23" t="n">
+        <v>1047.25</v>
       </c>
     </row>
     <row r="24">
@@ -1149,33 +1145,31 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Priya Raman</t>
+          <t>Tom Becker</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>CM-703853</t>
+          <t>LF-772292</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Marcus Novak</t>
+          <t>Hannah Haines</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Commercial</t>
+          <t>Life</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Renewal</t>
-        </is>
-      </c>
-      <c r="G24" t="inlineStr">
-        <is>
-          <t>$6,738.76</t>
-        </is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="G24" t="n">
+        <v>1282.93</v>
       </c>
     </row>
     <row r="25">
@@ -1184,22 +1178,22 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>TOM BECKER</t>
+          <t>Tom Becker</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>HO-214682</t>
+          <t>LF-823405</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Olivia Delgado</t>
+          <t>Isaac Holloway</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t xml:space="preserve">Home </t>
+          <t>Life</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1208,26 +1202,26 @@
         </is>
       </c>
       <c r="G25" t="n">
-        <v>3227.55</v>
+        <v>900.96</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Tom Becker</t>
+          <t>Aisha Bello</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>HO-776364</t>
+          <t>HO-904722</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Owen Petrov</t>
+          <t>Victor Castillo</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
@@ -1237,44 +1231,44 @@
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>RENEWAL</t>
+          <t>Renewal</t>
         </is>
       </c>
       <c r="G26" t="n">
-        <v>1228.74</v>
+        <v>3497.88</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Tom Becker</t>
+          <t>Grant Fowler</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>HO-825309</t>
+          <t>AU-647128</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Felix Lindqvist</t>
+          <t>Samuel Ruiz</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Home</t>
+          <t>Auto</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Renewal</t>
+          <t>New</t>
         </is>
       </c>
       <c r="G27" t="n">
-        <v>2167.76</v>
+        <v>910.76</v>
       </c>
     </row>
     <row r="28">
@@ -1283,22 +1277,22 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Grant Fowler</t>
+          <t>Maya Chen</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>LF-524723</t>
+          <t>AU-327854</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>Marcus Novak</t>
+          <t>Elena Mbeki</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Life</t>
+          <t>Auto</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1307,43 +1301,11 @@
         </is>
       </c>
       <c r="G28" t="n">
-        <v>1038.41</v>
+        <v>2269.5</v>
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="2" t="n">
-        <v>46289</v>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>Luis Ortega</t>
-        </is>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>HO-809922</t>
-        </is>
-      </c>
-      <c r="D29" t="inlineStr">
-        <is>
-          <t>Felix Lindqvist</t>
-        </is>
-      </c>
-      <c r="E29" t="inlineStr">
-        <is>
-          <t>Home</t>
-        </is>
-      </c>
-      <c r="F29" t="inlineStr">
-        <is>
-          <t>New</t>
-        </is>
-      </c>
-      <c r="G29" t="inlineStr">
-        <is>
-          <t>$2,290.06</t>
-        </is>
-      </c>
+      <c r="A29" s="2" t="n"/>
     </row>
     <row r="30">
       <c r="A30" s="2" t="n">
@@ -1351,22 +1313,22 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Priya Raman</t>
+          <t>Maya Chen</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>CM-417543</t>
+          <t>LF-747769</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>Zoe Marsh</t>
+          <t>Hannah Haines</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Commercial</t>
+          <t>Life</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -1375,40 +1337,40 @@
         </is>
       </c>
       <c r="G30" t="n">
-        <v>3638.9</v>
+        <v>889.85</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="n">
-        <v>46290</v>
+        <v>46289</v>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Priya Raman</t>
+          <t>tom becker</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>CM-309505</t>
+          <t>LF-900308</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>Maria Moreau</t>
+          <t>Grace Albright</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t xml:space="preserve">Commercial </t>
+          <t>Life</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Renewal</t>
+          <t>New</t>
         </is>
       </c>
       <c r="G31" t="n">
-        <v>9002.15</v>
+        <v>2292.38</v>
       </c>
     </row>
     <row r="32">
@@ -1417,22 +1379,22 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Tom Becker</t>
+          <t>grant fowler</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>AU-332785</t>
+          <t>HO-466956</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>Jonah Calloway</t>
+          <t>Olivia Delgado</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Auto</t>
+          <t>Home</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -1441,7 +1403,7 @@
         </is>
       </c>
       <c r="G32" t="n">
-        <v>1098.02</v>
+        <v>1946.2</v>
       </c>
     </row>
     <row r="33">
@@ -1455,12 +1417,12 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>AU-585556</t>
+          <t>AU-113340</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>Maria Novak</t>
+          <t>Ruby Sorensen</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
@@ -1474,18 +1436,51 @@
         </is>
       </c>
       <c r="G33" t="n">
-        <v>1546.35</v>
+        <v>1226.71</v>
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="2" t="n"/>
+      <c r="A34" s="2" t="n">
+        <v>46290</v>
+      </c>
       <c r="B34" t="inlineStr">
         <is>
+          <t>Tom Becker</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>AU-123182</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>Ivy Okafor</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>Auto</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="G34" t="n">
+        <v>2376.39</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="2" t="n"/>
+      <c r="B35" t="inlineStr">
+        <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="G34" t="n">
-        <v>76928.11</v>
+      <c r="G35" t="n">
+        <v>69803.75999999999</v>
       </c>
     </row>
   </sheetData>
@@ -1537,16 +1532,16 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>CM-212214</t>
+          <t>LF-747769</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Commercial</t>
+          <t>Life</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>8413.530000000001</v>
+        <v>875.08</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
@@ -1562,20 +1557,20 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>HO-471658</t>
+          <t>AU-869957</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Home</t>
+          <t>Auto</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>1630.08</v>
+        <v>1952.94</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Renewed</t>
+          <t>Lost</t>
         </is>
       </c>
     </row>
@@ -1587,16 +1582,16 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>HO-831105</t>
+          <t>AU-327854</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Home</t>
+          <t>Auto</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>1610.74</v>
+        <v>2182.11</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
@@ -1612,16 +1607,16 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>AU-679549</t>
+          <t>HO-384580</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Auto</t>
+          <t>Home</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>1468.9</v>
+        <v>2787.21</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
@@ -1637,7 +1632,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>HO-922478</t>
+          <t>HO-569426</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1646,7 +1641,7 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>2011.21</v>
+        <v>2996.04</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
@@ -1662,16 +1657,16 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>AU-694316</t>
+          <t>HO-916146</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Auto</t>
+          <t>Home</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>2202.18</v>
+        <v>2840.54</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
@@ -1687,41 +1682,41 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>LF-134500</t>
+          <t>AU-842517</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Life</t>
+          <t>Auto</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>1670.67</v>
+        <v>1072.07</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Renewed</t>
+          <t>Lost</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Luis Ortega</t>
+          <t>Priya Raman</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>HO-847332</t>
+          <t>CM-111619</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Home</t>
+          <t>Commercial</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>2679.73</v>
+        <v>2970.04</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
@@ -1737,7 +1732,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>CM-703853</t>
+          <t>CM-967377</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1746,7 +1741,7 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>6613.87</v>
+        <v>7870.46</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
@@ -1762,16 +1757,16 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>CM-309505</t>
+          <t>LF-744413</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Commercial</t>
+          <t>Life</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>8558.440000000001</v>
+        <v>2181.48</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
@@ -1787,7 +1782,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>LF-842776</t>
+          <t>LF-711698</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1796,7 +1791,7 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>1477.08</v>
+        <v>957.99</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
@@ -1812,16 +1807,16 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>CM-417543</t>
+          <t>LF-163440</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Commercial</t>
+          <t>Life</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>3404.66</v>
+        <v>810.3200000000001</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
@@ -1837,16 +1832,16 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>HO-825309</t>
+          <t>LF-823405</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Home</t>
+          <t>Life</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>2222.17</v>
+        <v>876.27</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
@@ -1862,16 +1857,16 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>HO-214682</t>
+          <t>AU-113340</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Home</t>
+          <t>Auto</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>3020.24</v>
+        <v>1119.95</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
@@ -1882,12 +1877,12 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Tom Becker</t>
+          <t>Aisha Bello</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>HO-776364</t>
+          <t>HO-590156</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1896,7 +1891,7 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>1193.02</v>
+        <v>1744.4</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
@@ -1907,21 +1902,21 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Tom Becker</t>
+          <t>Aisha Bello</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>AU-332785</t>
+          <t>HO-904722</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Auto</t>
+          <t>Home</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>1047.91</v>
+        <v>3169.89</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
@@ -1932,12 +1927,12 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Tom Becker</t>
+          <t>Aisha Bello</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>AU-585556</t>
+          <t>AU-569417</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1946,7 +1941,7 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>1461.18</v>
+        <v>1160.41</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
@@ -1962,16 +1957,16 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>HO-190025</t>
+          <t>AU-917151</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Home</t>
+          <t>Auto</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>1720.41</v>
+        <v>959.37</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
@@ -1982,21 +1977,21 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Aisha Bello</t>
+          <t>Grant Fowler</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>AU-316916</t>
+          <t>HO-545336</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Auto</t>
+          <t>Home</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>1583</v>
+        <v>1106.26</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
@@ -2012,16 +2007,16 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>LF-524723</t>
+          <t>AU-445474</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Life</t>
+          <t>Auto</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>1040.53</v>
+        <v>1250.08</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
@@ -2037,16 +2032,16 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>AU-306909</t>
+          <t>HO-466956</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Auto</t>
+          <t>Home</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>1821.16</v>
+        <v>1747.05</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
